--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6932281-9DC5-E44A-8648-133058B4D585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1E2559-6859-2942-98CF-D1D5519FB434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4260" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
   <si>
     <t>Date de naissance</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Marc Thomas</t>
+  </si>
+  <si>
+    <t>Glenn Manga-Tabi</t>
   </si>
 </sst>
 </file>
@@ -570,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC62179-91BA-B241-B8B8-EFBF1E6AE721}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -915,6 +918,11 @@
         <v>46</v>
       </c>
     </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
